--- a/AAII_Financials/Quarterly/DOCN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DOCN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="92">
   <si>
     <t>DOCN</t>
   </si>
@@ -656,416 +656,429 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>281200</v>
+      </c>
+      <c r="E8" s="3">
         <v>257900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>242400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>229600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>218700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>210700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>204900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>198500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>192500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>184700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>180900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>177100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>169800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>165100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>163000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>152100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>133900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>127300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>119700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>111400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>103800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>93700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>87500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>81200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>76900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>72800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>69300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>65300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>61900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>58300</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>126500</v>
+      </c>
+      <c r="E9" s="3">
         <v>113200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>100100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>92700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>87800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>81300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>78800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>81900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>78300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>75600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>85800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>70300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>67400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>71900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>60200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>56700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>47800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>47200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>44400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>43500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>43100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>39500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>38600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>37100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>35200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>34700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>33000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>30900</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>29900</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>28500</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>154700</v>
+      </c>
+      <c r="E10" s="3">
         <v>144700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>142300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>136900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>130900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>129400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>126100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>116600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>114100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>109100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>95000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>106700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>102500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>93300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>102800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>95400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>86100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>80100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>75300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>67900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>60700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>54200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>48900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>44100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>41700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>38100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>36300</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>34400</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>32000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>29800</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1098,100 +1111,104 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>57500</v>
+      </c>
+      <c r="E12" s="3">
         <v>48800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>44300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>38100</v>
-      </c>
-      <c r="G12" s="3">
-        <v>39600</v>
       </c>
       <c r="H12" s="3">
         <v>39600</v>
       </c>
       <c r="I12" s="3">
+        <v>39600</v>
+      </c>
+      <c r="J12" s="3">
         <v>39500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>36300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>33000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>32900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>27400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>32600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>38600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>38300</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>39400</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>30200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>37000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>37200</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>36200</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>29900</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>27100</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>22400</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>20700</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>19700</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>15100</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>19500</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>15300</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>16600</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>14600</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>13500</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1282,53 +1299,56 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="E14" s="3">
+        <v>2700</v>
+      </c>
+      <c r="F14" s="3">
         <v>-300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-48400</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>300</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J14" s="3">
         <v>-500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>3200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>3700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>10700</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>12500</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>8100</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>7400</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>28500</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
@@ -1336,11 +1356,11 @@
         <v>0</v>
       </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>400</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
       <c r="V14" s="3">
         <v>0</v>
       </c>
@@ -1348,25 +1368,25 @@
         <v>0</v>
       </c>
       <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
         <v>3400</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>300</v>
       </c>
-      <c r="Z14" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AA14" s="3" t="s">
         <v>10</v>
       </c>
       <c r="AB14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD14" s="3" t="s">
-        <v>10</v>
+      <c r="AC14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD14" s="3">
+        <v>0</v>
       </c>
       <c r="AE14" s="3" t="s">
         <v>10</v>
@@ -1374,53 +1394,56 @@
       <c r="AF14" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>47300</v>
+      </c>
+      <c r="E15" s="3">
         <v>41900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>36800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>33000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>30600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>27000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>25800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>34200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>31700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>30400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>29200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>28600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>25500</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>26200</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1466,8 +1489,11 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,192 +1523,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>251800</v>
+      </c>
+      <c r="E17" s="3">
         <v>221300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>203600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>184700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>183100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>173100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>170400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>170700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>166400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>165000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>159700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>133500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>163900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>169700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>174400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>144900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>141800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>141300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>129800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>113100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>106400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>93800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>86100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>87900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>75100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>85300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>75600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>73000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>68300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>67900</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>29400</v>
+      </c>
+      <c r="E18" s="3">
         <v>36600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>38800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>44900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>35600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>37600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>34600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>27800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>26000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>19700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>21200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>43600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>5900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-4600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-11400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>7200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-7900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-14000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-10100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-1700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-2600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-6700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-12500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-6300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-7700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-6400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-9600</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,169 +1748,173 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E20" s="3">
+        <v>1700</v>
+      </c>
+      <c r="F20" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="G20" s="3">
+        <v>600</v>
+      </c>
+      <c r="H20" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="I20" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="J20" s="3">
+        <v>400</v>
+      </c>
+      <c r="K20" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="L20" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="M20" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="N20" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="O20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="P20" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>300</v>
+      </c>
+      <c r="R20" s="3">
         <v>4400</v>
       </c>
-      <c r="E20" s="3">
-        <v>-7500</v>
-      </c>
-      <c r="F20" s="3">
-        <v>600</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-8000</v>
-      </c>
-      <c r="H20" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="I20" s="3">
-        <v>400</v>
-      </c>
-      <c r="J20" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="K20" s="3">
+      <c r="S20" s="3">
+        <v>3300</v>
+      </c>
+      <c r="T20" s="3">
+        <v>2100</v>
+      </c>
+      <c r="U20" s="3">
+        <v>800</v>
+      </c>
+      <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="X20" s="3">
+        <v>200</v>
+      </c>
+      <c r="Y20" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-1600</v>
       </c>
-      <c r="L20" s="3">
-        <v>-4200</v>
-      </c>
-      <c r="M20" s="3">
-        <v>-10000</v>
-      </c>
-      <c r="N20" s="3">
-        <v>1000</v>
-      </c>
-      <c r="O20" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="P20" s="3">
-        <v>300</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>4400</v>
-      </c>
-      <c r="R20" s="3">
-        <v>3300</v>
-      </c>
-      <c r="S20" s="3">
-        <v>2100</v>
-      </c>
-      <c r="T20" s="3">
-        <v>800</v>
-      </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
-      <c r="V20" s="3">
-        <v>-100</v>
-      </c>
-      <c r="W20" s="3">
-        <v>200</v>
-      </c>
-      <c r="X20" s="3">
-        <v>100</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-3700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-4100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-3700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>6300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-2700</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-2100</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>74100</v>
+        <v>75500</v>
       </c>
       <c r="E21" s="3">
+        <v>76800</v>
+      </c>
+      <c r="F21" s="3">
         <v>83100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>77300</v>
       </c>
-      <c r="G21" s="3">
-        <v>74300</v>
-      </c>
       <c r="H21" s="3">
+        <v>72400</v>
+      </c>
+      <c r="I21" s="3">
         <v>66900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>60000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>64400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>59300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>54300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>60400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>71100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>32600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>21300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>21400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>36100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>18500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>10800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>13300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>20600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>19200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>20900</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Z21" s="3" t="s">
         <v>10</v>
       </c>
@@ -1899,22 +1936,25 @@
       <c r="AF21" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG21" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E22" s="3">
         <v>10600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>8500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>5000</v>
-      </c>
-      <c r="G22" s="3">
-        <v>2200</v>
       </c>
       <c r="H22" s="3">
         <v>2200</v>
@@ -1923,7 +1963,7 @@
         <v>2200</v>
       </c>
       <c r="J22" s="3">
-        <v>2300</v>
+        <v>2200</v>
       </c>
       <c r="K22" s="3">
         <v>2300</v>
@@ -1938,13 +1978,13 @@
         <v>2300</v>
       </c>
       <c r="O22" s="3">
+        <v>2300</v>
+      </c>
+      <c r="P22" s="3">
         <v>2100</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>2200</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>2100</v>
       </c>
       <c r="R22" s="3">
         <v>2100</v>
@@ -1956,227 +1996,236 @@
         <v>2100</v>
       </c>
       <c r="U22" s="3">
+        <v>2100</v>
+      </c>
+      <c r="V22" s="3">
         <v>1100</v>
-      </c>
-      <c r="V22" s="3">
-        <v>200</v>
       </c>
       <c r="W22" s="3">
         <v>200</v>
       </c>
       <c r="X22" s="3">
+        <v>200</v>
+      </c>
+      <c r="Y22" s="3">
         <v>2300</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>13600</v>
       </c>
-      <c r="Z22" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AA22" s="3" t="s">
         <v>10</v>
       </c>
       <c r="AB22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AC22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD22" s="3">
         <v>9400</v>
       </c>
-      <c r="AD22" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AE22" s="3" t="s">
         <v>10</v>
       </c>
       <c r="AF22" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>27100</v>
+      </c>
+      <c r="E23" s="3">
         <v>24500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>32500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>90300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>42400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>41400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>29000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>29600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>24800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>14300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>13500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>37100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>4000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-27900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-9100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>8300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-7900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-15200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-11200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-2000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-2700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-2300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-13800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-10300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-2300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-16200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-9300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-10400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-8500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-11400</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="E24" s="3">
         <v>8700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>6900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-68100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>5400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>3200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>10700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-3300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>5700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-2400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>17900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>3300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-11500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-1200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>3300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1000</v>
       </c>
-      <c r="Y24" s="3">
-        <v>0</v>
-      </c>
       <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="3">
         <v>-100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>200</v>
-      </c>
-      <c r="AE24" s="3">
-        <v>100</v>
       </c>
       <c r="AF24" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG24" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,192 +2316,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>35400</v>
+      </c>
+      <c r="E26" s="3">
         <v>15800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>25700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>158400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>37000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>38200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>18300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>32900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>19100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>14100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>15900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>19200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-16400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-10400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>7900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-6800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-18600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-12100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-1900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-2200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-3300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-13900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-10200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-2600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-16900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-9600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-10600</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-8700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-11500</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>35400</v>
+      </c>
+      <c r="E27" s="3">
         <v>15800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>25700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>158400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>37000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>38200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>18300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>32900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>19100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>14100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>15900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>19200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-16400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-10400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>7900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-6800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-18600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-12100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-1900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-2200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-3300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-13900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-10200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-2600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-16900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-9600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-10600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-8700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-11500</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2601,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2635,8 +2696,11 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2791,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,192 +2886,201 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="F32" s="3">
+        <v>7500</v>
+      </c>
+      <c r="G32" s="3">
+        <v>-600</v>
+      </c>
+      <c r="H32" s="3">
+        <v>6100</v>
+      </c>
+      <c r="I32" s="3">
+        <v>2300</v>
+      </c>
+      <c r="J32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="K32" s="3">
+        <v>2300</v>
+      </c>
+      <c r="L32" s="3">
+        <v>1600</v>
+      </c>
+      <c r="M32" s="3">
+        <v>4200</v>
+      </c>
+      <c r="N32" s="3">
+        <v>10000</v>
+      </c>
+      <c r="O32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="P32" s="3">
+        <v>1200</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="R32" s="3">
         <v>-4400</v>
       </c>
-      <c r="E32" s="3">
-        <v>7500</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-600</v>
-      </c>
-      <c r="G32" s="3">
-        <v>8000</v>
-      </c>
-      <c r="H32" s="3">
-        <v>2300</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-400</v>
-      </c>
-      <c r="J32" s="3">
-        <v>2300</v>
-      </c>
-      <c r="K32" s="3">
+      <c r="S32" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="T32" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="U32" s="3">
+        <v>-800</v>
+      </c>
+      <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
+        <v>100</v>
+      </c>
+      <c r="X32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Y32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Z32" s="3">
         <v>1600</v>
       </c>
-      <c r="L32" s="3">
-        <v>4200</v>
-      </c>
-      <c r="M32" s="3">
-        <v>10000</v>
-      </c>
-      <c r="N32" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="O32" s="3">
-        <v>1200</v>
-      </c>
-      <c r="P32" s="3">
-        <v>-300</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>-4400</v>
-      </c>
-      <c r="R32" s="3">
-        <v>-3300</v>
-      </c>
-      <c r="S32" s="3">
-        <v>-2100</v>
-      </c>
-      <c r="T32" s="3">
-        <v>-800</v>
-      </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
-      <c r="V32" s="3">
-        <v>100</v>
-      </c>
-      <c r="W32" s="3">
-        <v>-200</v>
-      </c>
-      <c r="X32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>1600</v>
-      </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>3700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>4100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>3700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-6300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>2700</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>2100</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>35400</v>
+      </c>
+      <c r="E33" s="3">
         <v>15800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>25700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>158400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>37000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>38200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>18300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>32900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>19100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>14100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>15900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>19200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-16400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-10400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>7900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-6800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-18600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-12100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-1900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-2200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-3300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-13900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-10200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-2600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-16900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-9600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-10600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-8700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-11500</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,197 +3171,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>35400</v>
+      </c>
+      <c r="E35" s="3">
         <v>15800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>25700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>158400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>37000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>38200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>18300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>32900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>19100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>14100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>15900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>19200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-16400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-10400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>7900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-6800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-18600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-12100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-1900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-2200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-3300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-13900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-10200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-2600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-16900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-9600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-10600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-8700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-11500</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3403,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,77 +3438,78 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>767000</v>
+      </c>
+      <c r="E41" s="3">
         <v>741400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>254500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>236600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>387700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>360400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>428400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>439900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>443100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>419100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>317200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>79400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>120000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>20900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>140800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>24100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>72200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>464800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1713400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>589800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>577200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>560100</v>
       </c>
-      <c r="Y41" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Z41" s="3" t="s">
         <v>10</v>
       </c>
@@ -3438,14 +3525,17 @@
       <c r="AD41" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AE41" s="3">
-        <v>0</v>
+      <c r="AE41" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AF41" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3477,32 +3567,32 @@
         <v>0</v>
       </c>
       <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
         <v>94500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>304700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>430500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>591700</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>723500</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>800500</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>1094000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>1090400</v>
       </c>
-      <c r="U42" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="V42" s="3" t="s">
         <v>10</v>
       </c>
@@ -3518,8 +3608,8 @@
       <c r="Z42" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AA42" s="3">
-        <v>0</v>
+      <c r="AA42" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AB42" s="3">
         <v>0</v>
@@ -3536,77 +3626,80 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>115000</v>
+      </c>
+      <c r="E43" s="3">
         <v>105500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>118800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>84400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>81300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>76600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>91100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>88300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>67400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>63900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>74800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>60200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>57100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>55000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>53800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>59800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>44100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>42500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>39600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>42600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>33900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>28900</v>
       </c>
-      <c r="Y43" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Z43" s="3" t="s">
         <v>10</v>
       </c>
@@ -3622,14 +3715,17 @@
       <c r="AD43" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AE43" s="3">
-        <v>0</v>
+      <c r="AE43" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AF43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3672,8 +3768,8 @@
       <c r="P44" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -3720,77 +3816,80 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E45" s="3">
+      <c r="D45" s="3">
+        <v>46000</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F45" s="3">
         <v>5200</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="G45" s="3" t="s">
         <v>10</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I45" s="3">
+      <c r="I45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J45" s="3">
         <v>1600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>5000</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="L45" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N45" s="3">
         <v>1400</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="O45" s="3" t="s">
         <v>10</v>
       </c>
       <c r="P45" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="Q45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R45" s="3">
         <v>27900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>23900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>20900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>14200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>17100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>10400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>18000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>18300</v>
       </c>
-      <c r="Y45" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Z45" s="3" t="s">
         <v>10</v>
       </c>
@@ -3806,83 +3905,86 @@
       <c r="AD45" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AE45" s="3">
-        <v>0</v>
+      <c r="AE45" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AF45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1017600</v>
+      </c>
+      <c r="E46" s="3">
         <v>944300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>427000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>367600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>509800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>479200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>541700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>552000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>543700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>515800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>503000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>471500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>642100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>698600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>946000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>908400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1231100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1611900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1770100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>642800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>629100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>607300</v>
       </c>
-      <c r="Y46" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Z46" s="3" t="s">
         <v>10</v>
       </c>
@@ -3898,14 +4000,17 @@
       <c r="AD46" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AE46" s="3">
-        <v>0</v>
+      <c r="AE46" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AF46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3948,8 +4053,8 @@
       <c r="P47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -3996,77 +4101,80 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1555000</v>
+      </c>
+      <c r="E48" s="3">
         <v>973000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>749700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>781300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>717100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>671200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>533300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>473800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>489000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>466800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>445900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>436700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>422000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>446800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>426900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>271000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>268400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>259400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>249600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>241100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>243100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>242700</v>
       </c>
-      <c r="Y48" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Z48" s="3" t="s">
         <v>10</v>
       </c>
@@ -4082,82 +4190,85 @@
       <c r="AD48" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AE48" s="3">
-        <v>0</v>
+      <c r="AE48" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AF48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>444000</v>
+      </c>
+      <c r="E49" s="3">
         <v>557700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>558400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>472400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>475500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>480200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>553500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>490400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>494300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>494000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>503200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>508600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>425800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>430500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>434100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>437700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>84400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>78600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>75100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>75400</v>
-      </c>
-      <c r="W49" s="3">
-        <v>37200</v>
       </c>
       <c r="X49" s="3">
         <v>37200</v>
       </c>
-      <c r="Y49" s="3" t="s">
-        <v>10</v>
+      <c r="Y49" s="3">
+        <v>37200</v>
       </c>
       <c r="Z49" s="3" t="s">
         <v>10</v>
@@ -4174,14 +4285,17 @@
       <c r="AD49" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AE49" s="3">
-        <v>0</v>
+      <c r="AE49" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AF49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4386,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,77 +4481,80 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>12400</v>
+      </c>
+      <c r="E52" s="3">
         <v>11600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>12300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>10400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>16800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>10500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>10300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>8200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>7900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>7000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>6900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>7600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>7200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>7300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>8700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>6600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>6800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>6900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>6200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>6500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>6100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>6000</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Z52" s="3" t="s">
         <v>10</v>
       </c>
@@ -4450,14 +4570,17 @@
       <c r="AD52" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AE52" s="3">
-        <v>0</v>
+      <c r="AE52" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AF52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,77 +4671,80 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3123100</v>
+      </c>
+      <c r="E54" s="3">
         <v>2570400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1837700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1725700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1719800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1641700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1639000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1526500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1536800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1485600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1461000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1425100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1497900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1584000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1815600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1623700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1590700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1956800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2101000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>965800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>915400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>893300</v>
       </c>
-      <c r="Y54" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Z54" s="3" t="s">
         <v>10</v>
       </c>
@@ -4634,14 +4760,17 @@
       <c r="AD54" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AE54" s="3">
-        <v>0</v>
+      <c r="AE54" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AF54" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG54" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4803,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,77 +4838,78 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E57" s="3">
         <v>31900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>38800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>67600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>31300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>9400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>54600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>12900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>9500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>4500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>14300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>9600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>11000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>21100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>11800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>17800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>16300</v>
-      </c>
-      <c r="U57" s="3">
-        <v>12700</v>
       </c>
       <c r="V57" s="3">
         <v>12700</v>
       </c>
       <c r="W57" s="3">
+        <v>12700</v>
+      </c>
+      <c r="X57" s="3">
         <v>16200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>15100</v>
       </c>
-      <c r="Y57" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Z57" s="3" t="s">
         <v>10</v>
       </c>
@@ -4794,59 +4925,62 @@
       <c r="AD57" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AE57" s="3">
-        <v>0</v>
+      <c r="AE57" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AF57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>567700</v>
+      </c>
+      <c r="E58" s="3">
         <v>480100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>464600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>148900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>98200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>92900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>79300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>68100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>74000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>81200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>86500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>76100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>71700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>73100</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
@@ -4892,77 +5026,80 @@
       <c r="AF58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>127200</v>
+      </c>
+      <c r="E59" s="3">
         <v>103400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>19700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>61900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>60200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>53200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>12800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>66900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>80900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>78800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>29800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>69100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>58100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>48200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>190300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>87000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>56500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>46100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>45600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>44900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>39200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>30900</v>
       </c>
-      <c r="Y59" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Z59" s="3" t="s">
         <v>10</v>
       </c>
@@ -4978,83 +5115,86 @@
       <c r="AD59" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AE59" s="3">
-        <v>0</v>
+      <c r="AE59" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AF59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>776100</v>
+      </c>
+      <c r="E60" s="3">
         <v>647000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>619500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>325000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>224500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>198300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>221000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>176000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>220200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>189000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>192600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>184300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>167300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>170500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>165500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>98800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>74200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>62500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>58200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>57600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>55400</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>46000</v>
       </c>
-      <c r="Y60" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Z60" s="3" t="s">
         <v>10</v>
       </c>
@@ -5070,74 +5210,77 @@
       <c r="AD60" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AE60" s="3">
-        <v>0</v>
+      <c r="AE60" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AF60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1410200</v>
+      </c>
+      <c r="E61" s="3">
         <v>1027900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1236700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1465800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1665900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1649600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1616900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1557000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1564600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1574900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1573500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1583100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1587400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1605200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1470300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1468400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1466500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1464500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1462700</v>
       </c>
-      <c r="V61" s="3">
-        <v>0</v>
-      </c>
       <c r="W61" s="3">
         <v>0</v>
       </c>
@@ -5168,20 +5311,23 @@
       <c r="AF61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E62" s="3">
         <v>4100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>6200</v>
       </c>
-      <c r="F62" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="G62" s="3" t="s">
         <v>10</v>
       </c>
@@ -5191,54 +5337,54 @@
       <c r="I62" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J62" s="3">
+      <c r="J62" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K62" s="3">
         <v>1600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>4300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>5000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>9800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>5500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>6500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>132300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>26300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>2000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>2100</v>
       </c>
-      <c r="Y62" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Z62" s="3" t="s">
         <v>10</v>
       </c>
@@ -5254,14 +5400,17 @@
       <c r="AD62" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AE62" s="3">
-        <v>0</v>
+      <c r="AE62" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AF62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5501,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5596,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,77 +5691,80 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2192300</v>
+      </c>
+      <c r="E66" s="3">
         <v>1683000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1866400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1795300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1895000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1852400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1842000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1738200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1790600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1771600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1774700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1783900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1765500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1786600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1768100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1593500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1542400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1529000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1522800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>59400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>57300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>48200</v>
       </c>
-      <c r="Y66" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Z66" s="3" t="s">
         <v>10</v>
       </c>
@@ -5622,14 +5780,17 @@
       <c r="AD66" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AE66" s="3">
-        <v>0</v>
+      <c r="AE66" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AF66" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG66" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5823,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +5916,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6011,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5938,8 +6106,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,77 +6201,80 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-28000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-43700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-69400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-183500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-220500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-258700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-277000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-310000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-330100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-344200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-357800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-266600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-230700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-214300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-200800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-210900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-204700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-186500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-174400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-172600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-170400</v>
       </c>
-      <c r="Y72" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Z72" s="3" t="s">
         <v>10</v>
       </c>
@@ -6116,14 +6290,17 @@
       <c r="AD72" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AE72" s="3">
-        <v>0</v>
+      <c r="AE72" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AF72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6391,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6486,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,77 +6581,80 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>930700</v>
+      </c>
+      <c r="E76" s="3">
         <v>887400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-28700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-69600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-175200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-210700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-203000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-211700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-253800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-286100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-313700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-358800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-267600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-202600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>47600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>30200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>48300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>427800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>578200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>906400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>858100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>845100</v>
       </c>
-      <c r="Y76" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Z76" s="3" t="s">
         <v>10</v>
       </c>
@@ -6484,14 +6670,17 @@
       <c r="AD76" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AE76" s="3">
-        <v>0</v>
+      <c r="AE76" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AF76" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG76" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,197 +6771,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>35400</v>
+      </c>
+      <c r="E81" s="3">
         <v>15800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>25700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>158400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>37000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>38200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>18300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>32900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>19100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>14100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>15900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>19200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-16400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-10400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>7900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-6800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-18600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-12100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-1900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-2200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-3300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-13900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-10200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-2600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-16900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-9600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-10600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-8700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-11500</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,77 +7003,78 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>25600</v>
+      </c>
+      <c r="E83" s="3">
         <v>21800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>20400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>28700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>26000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>24600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>23500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>15300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>25500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>26200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>21800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>20000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>21300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>20800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>28300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>25600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>24300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>23900</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>23500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>22400</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>21600</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>21000</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Z83" s="3" t="s">
         <v>10</v>
       </c>
@@ -6891,14 +7090,17 @@
       <c r="AD83" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AE83" s="3">
-        <v>0</v>
+      <c r="AE83" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AF83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7191,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7286,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7381,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7476,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,77 +7571,80 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>110000</v>
+      </c>
+      <c r="E89" s="3">
         <v>46900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>57300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>95800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>92400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>64100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>71300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>73400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>71300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>66700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>80500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>54100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>64200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>36200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>62800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>55800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>46100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>30400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>32700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>40200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>40400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>19800</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Z89" s="3" t="s">
         <v>10</v>
       </c>
@@ -7443,14 +7660,17 @@
       <c r="AD89" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AE89" s="3">
-        <v>0</v>
+      <c r="AE89" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AF89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,77 +7703,78 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-81300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-51800</v>
       </c>
-      <c r="E91" s="3">
-        <v>-26200</v>
-      </c>
       <c r="F91" s="3">
+        <v>-153000</v>
+      </c>
+      <c r="G91" s="3">
         <v>-7800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-33200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-62000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-45300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-57400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-31900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-43700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-52200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-20200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-23500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-23300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-29000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-33300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-34000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-29300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-32700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-26700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-26000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-1400</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Z91" s="3" t="s">
         <v>10</v>
       </c>
@@ -7569,14 +7790,17 @@
       <c r="AD91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AE91" s="3">
-        <v>0</v>
+      <c r="AE91" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AF91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +7891,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,77 +7986,80 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-89100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-60600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-129500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-38400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-35400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-65000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-47100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-59800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-34400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>46400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>152900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>4600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>135800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>108000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>51600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-40600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-38200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1121000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-32400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-31500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-26000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-23700</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Z94" s="3" t="s">
         <v>10</v>
       </c>
@@ -7845,14 +8075,17 @@
       <c r="AD94" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AE94" s="3">
-        <v>0</v>
+      <c r="AE94" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AF94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,8 +8118,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7929,8 +8163,8 @@
       <c r="P96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -7977,8 +8211,11 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8306,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8401,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,77 +8496,80 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E100" s="3">
         <v>500600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>90300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-210300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-29700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-67200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-35400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-16800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-12900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-11200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>4400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-108400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-100800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-264200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-52800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-399900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-157900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>1123100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>3900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>2700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>463600</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Z100" s="3" t="s">
         <v>10</v>
       </c>
@@ -8339,14 +8585,17 @@
       <c r="AD100" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AE100" s="3">
-        <v>0</v>
+      <c r="AE100" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AF100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8354,20 +8603,20 @@
         <v>0</v>
       </c>
       <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
         <v>-200</v>
       </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
       <c r="G101" s="3">
         <v>0</v>
       </c>
       <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
         <v>-100</v>
       </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
       <c r="J101" s="3">
         <v>0</v>
       </c>
@@ -8378,34 +8627,34 @@
         <v>0</v>
       </c>
       <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3">
         <v>100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-100</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
       <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3">
         <v>100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-200</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-100</v>
       </c>
-      <c r="T101" s="3">
-        <v>0</v>
-      </c>
-      <c r="U101" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="V101" s="3">
-        <v>0</v>
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+      <c r="V101" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="W101" s="3">
         <v>0</v>
@@ -8437,77 +8686,80 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>25700</v>
+      </c>
+      <c r="E102" s="3">
         <v>486900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>18100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-152900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>27300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-68000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-11400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-3200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>24000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>101800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>237900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-49800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>99200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-120100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>116700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-39000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-392800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-1248600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>1123400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>12500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>17200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>459700</v>
       </c>
-      <c r="Y102" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Z102" s="3" t="s">
         <v>10</v>
       </c>
@@ -8523,10 +8775,13 @@
       <c r="AD102" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AE102" s="3">
-        <v>0</v>
+      <c r="AE102" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AF102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG102" s="3">
         <v>0</v>
       </c>
     </row>
